--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:48:48+00:00</t>
+    <t>2026-03-19T07:57:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T07:57:25+00:00</t>
+    <t>2026-03-19T11:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T11:47:55+00:00</t>
+    <t>2026-03-20T10:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T10:04:21+00:00</t>
+    <t>2026-03-20T11:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:14:53+00:00</t>
+    <t>2026-03-20T11:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:25:24+00:00</t>
+    <t>2026-03-20T11:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:48:45+00:00</t>
+    <t>2026-03-20T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:42:40+00:00</t>
+    <t>2026-03-20T12:57:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:57:31+00:00</t>
+    <t>2026-03-20T13:17:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -941,7 +941,7 @@
     <t>PractitionerRole.organization.identifier.system</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/organization-it-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/organization-id-type-vs</t>
   </si>
   <si>
     <t>PractitionerRole.organization.identifier.value</t>
@@ -1481,7 +1481,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:17:08+00:00</t>
+    <t>2026-04-10T11:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:25:48+00:00</t>
+    <t>2026-04-10T11:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:43:13+00:00</t>
+    <t>2026-04-10T11:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:51:44+00:00</t>
+    <t>2026-04-10T12:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:03:27+00:00</t>
+    <t>2026-04-10T12:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:17:42+00:00</t>
+    <t>2026-04-10T12:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:43:41+00:00</t>
+    <t>2026-04-10T12:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:51:31+00:00</t>
+    <t>2026-04-10T13:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:11:24+00:00</t>
+    <t>2026-04-13T12:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:24:04+00:00</t>
+    <t>2026-04-13T13:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T13:08:41+00:00</t>
+    <t>2026-04-15T12:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/person-id-type-vs</t>
+    <t>http://hl7.no/fhir/ig/ParekIG/ValueSet/healthcare-person-id-type-vs</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -1481,7 +1481,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.6484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.21875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
+++ b/currentbuild/StructureDefinition-parek-practitioner-role.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
